--- a/manufacturing_forms/007_production_closure_checklist--manufacturing_forms.xlsx
+++ b/manufacturing_forms/007_production_closure_checklist--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,41 +520,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>production_closure_checklist_1</t>
+          <t>production_line</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Production Closure Checklist</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Production Line</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter the current production line</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>production_closure_checklist_2</t>
+          <t>is_production_line_closed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Production Line</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Is the production line closed?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter yes or no</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +574,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>production_closure_checklist_3</t>
+          <t>production_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -574,10 +582,14 @@
           <t>Production Date</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter the production date</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,7 +601,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>production_closure_checklist_4</t>
+          <t>production_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -597,10 +609,14 @@
           <t>Production Time</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter the production time</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,7 +628,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>production_closure_checklist_5</t>
+          <t>shift_length</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -620,10 +636,14 @@
           <t>Shift Length</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter the length of the shift</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>production_closure_checklist_6</t>
+          <t>is_shift_length_hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shift Length Unit</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Is the shift length in hours?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter yes or no</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,7 +682,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>production_closure_checklist_7</t>
+          <t>production_manager_name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -666,10 +690,14 @@
           <t>Production Manager</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter the production manager's name</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,7 +709,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>production_closure_checklist_8</t>
+          <t>production_manager_email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -689,10 +717,14 @@
           <t>Production Manager Email</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter the production manager's email</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,7 +736,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>production_closure_checklist_9</t>
+          <t>production_manager_phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -712,10 +744,14 @@
           <t>Production Manager Phone</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter the production manager's phone number</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>production_closure_checklist_10</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Production Manager</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter the production location</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,340 +790,49 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>production_closure_checklist_11</t>
+          <t>is_production_resources_available_next_shift</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Production Line</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Are any production resources available for next shift?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter yes or no</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>production_closure_checklist_12</t>
+          <t>is_production_resources_unavailable_next_shift</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Are any production resources unavailable for next shift?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter yes or no</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1101,7 +850,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>production_closure_checklist_2_choices</t>
+          <t>is_production_line_closed_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +892,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>production_closure_checklist_2_choices</t>
+          <t>is_production_line_closed_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +909,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>production_closure_checklist_6_choices</t>
+          <t>is_shift_length_hours_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +926,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>production_closure_checklist_6_choices</t>
+          <t>is_shift_length_hours_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +943,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>production_closure_checklist_11_choices</t>
+          <t>is_production_resources_available_next_shift_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +960,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>production_closure_checklist_11_choices</t>
+          <t>is_production_resources_available_next_shift_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +977,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>production_closure_checklist_12_choices</t>
+          <t>is_production_resources_unavailable_next_shift_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +994,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>production_closure_checklist_12_choices</t>
+          <t>is_production_resources_unavailable_next_shift_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
